--- a/your-code/PivotTable vs Formula Exercise.xlsx
+++ b/your-code/PivotTable vs Formula Exercise.xlsx
@@ -1,29 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c646aa9d978bc39d/Documents/Module 4/Week 1/Day 2 - Excel Pivot Tables and Macros/Lab/lab_2_Pivot-tables_vs_formulas/your-code/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3197619181886cd2/Documents/new_bootcamp/Week 20/Day 2/lab-excel-pivot-tables-vs-formulas/your-code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{A3A7DBBF-F3AC-4897-BE43-8F94BEB89478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7683A57F-D9F9-4F18-9995-6F2FB9CE459C}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{A3A7DBBF-F3AC-4897-BE43-8F94BEB89478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63314310-D327-46AD-A05C-170A23AA2CB7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Questions" sheetId="3" r:id="rId1"/>
-    <sheet name="data" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
+    <sheet name="data" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">data!$A$1:$E$39</definedName>
-    <definedName name="ARTÍCULOS" localSheetId="1">data!$A$1:$E$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">data!$A$1:$E$39</definedName>
+    <definedName name="ARTÍCULOS" localSheetId="2">data!$A$1:$E$38</definedName>
     <definedName name="ARTÍCULOS">#REF!</definedName>
     <definedName name="data">data!$A$1:$E$39</definedName>
     <definedName name="miLista">data!$A$1:$E$4500</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="90" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -41,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="73">
   <si>
     <t>China</t>
   </si>
@@ -231,15 +235,46 @@
   <si>
     <t>Lamp Base</t>
   </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Total Sum of Price</t>
+  </si>
+  <si>
+    <t>Sum of Price</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>Count of Section</t>
+  </si>
+  <si>
+    <t>Total Count of Section</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00[$€]_-;\-* #,##0.00[$€]_-;_-* &quot;-&quot;??[$€]_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="#,##0.00\ [$€-407]"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="MS Sans Serif"/>
@@ -260,6 +295,19 @@
       <sz val="10"/>
       <name val="MS Sans Serif"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -275,7 +323,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -298,12 +346,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -327,12 +386,144 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" pivotButton="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Euro" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -343,6 +534,6554 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[PivotTable vs Formula Exercise.xlsx]Sheet1!PivotTable13</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="13"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="14"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="15"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="16"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="17"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="18"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="19"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="20"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="21"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="22"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="23"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="24"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="25"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="26"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="27"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="28"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="29"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="30"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="31"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="32"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="33"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="34"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="35"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="36"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="37"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="38"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="39"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="40"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="41"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="42"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="43"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="44"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="45"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="46"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="47"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="48"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="49"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="50"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="51"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="52"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="53"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="54"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="55"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="56"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="57"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="58"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="59"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="60"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="61"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="62"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="63"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="64"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="65"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="66"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="67"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="68"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="69"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="70"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="71"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="72"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="73"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="74"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="75"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="76"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="77"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="78"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="79"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="80"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="81"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="82"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="83"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="84"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="85"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="86"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="87"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="88"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="89"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="90"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="91"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="92"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="93"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="94"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="95"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="96"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="97"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="98"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="99"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="100"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="101"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="102"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="103"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="104"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="105"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="106"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="107"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="108"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="109"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="110"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="111"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="112"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="113"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="114"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="115"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$3:$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2018 - Sum of Price</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$6:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>CERAMICS</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>CLOTHING</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>HARDWARE</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>SPORTS</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>TOYS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$6:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00[$€]_-;\-* #,##0.00[$€]_-;_-* "-"??[$€]_-;_-@_-</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>168.00692365944252</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>902.13118892214493</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>71.15983315903982</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2398.7595110165521</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>507.12800355799163</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000006F-C12E-4D4D-91D1-8AAB9B7F8B24}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$3:$C$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2018 - Count of Section</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$6:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>CERAMICS</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>CLOTHING</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>HARDWARE</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>SPORTS</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>TOYS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$6:$C$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000070-C12E-4D4D-91D1-8AAB9B7F8B24}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$3:$D$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2019 - Sum of Price</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$6:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>CERAMICS</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>CLOTHING</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>HARDWARE</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>SPORTS</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>TOYS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$6:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00[$€]_-;\-* #,##0.00[$€]_-;_-* "-"??[$€]_-;_-@_-</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>200.6171141802796</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>562.87788636063124</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>33.494404577308188</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>194.70989145721396</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>368.78703737093264</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000071-C12E-4D4D-91D1-8AAB9B7F8B24}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$3:$E$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2019 - Count of Section</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$6:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>CERAMICS</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>CLOTHING</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>HARDWARE</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>SPORTS</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>TOYS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$6:$E$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000072-C12E-4D4D-91D1-8AAB9B7F8B24}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="524934672"/>
+        <c:axId val="524933232"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="524934672"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="524933232"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="524933232"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_-* #,##0.00[$€]_-;\-* #,##0.00[$€]_-;_-* &quot;-&quot;??[$€]_-;_-@_-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="524934672"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -397,6 +7136,893 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C87A7DFC-BC35-5EC0-8B0A-C79B14E99DBB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Rami Abdalla" refreshedDate="46112.088713541663" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="38" xr:uid="{11D40041-33BB-4B04-BF57-957A342382E9}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:E39" sheet="data"/>
+  </cacheSource>
+  <cacheFields count="8">
+    <cacheField name="Section" numFmtId="0">
+      <sharedItems count="5">
+        <s v="CERAMICS"/>
+        <s v="CLOTHING"/>
+        <s v="SPORTS"/>
+        <s v="HARDWARE"/>
+        <s v="TOYS"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Item" numFmtId="0">
+      <sharedItems count="37">
+        <s v="Pipes"/>
+        <s v="Decorative Plate"/>
+        <s v="Tea Set"/>
+        <s v="Ashtray"/>
+        <s v="Flower Pot"/>
+        <s v="China Pitcher"/>
+        <s v="Men's Card"/>
+        <s v="Women's Pants"/>
+        <s v="Men's Shirt"/>
+        <s v="Women's Blouse"/>
+        <s v="Leather Jacket"/>
+        <s v="Men's Coat"/>
+        <s v="Women's Coat"/>
+        <s v="Leather Belt"/>
+        <s v="Tennis Racket"/>
+        <s v="Tracksuit"/>
+        <s v="Electric Train"/>
+        <s v="Olympic Pistol"/>
+        <s v="Skateboard"/>
+        <s v="Basketball"/>
+        <s v="Soccer Ball"/>
+        <s v="Sweatshirt"/>
+        <s v="Mountain Bike"/>
+        <s v="Screwdriver"/>
+        <s v="Handsaw"/>
+        <s v="Wrench"/>
+        <s v="Pliers"/>
+        <s v="Hammer"/>
+        <s v="Large File"/>
+        <s v="Drill Bit Set"/>
+        <s v="Remote Control Car"/>
+        <s v="Walker"/>
+        <s v="Video Game Console"/>
+        <s v="Walking Doll"/>
+        <s v="Soldier Fort"/>
+        <s v="Sound Gun"/>
+        <s v="Lamp Base"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Date" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2018-05-12T00:00:00" maxDate="2019-01-30T00:00:00" count="37">
+        <d v="2019-01-27T00:00:00"/>
+        <d v="2018-12-24T00:00:00"/>
+        <d v="2019-01-15T00:00:00"/>
+        <d v="2018-05-12T00:00:00"/>
+        <d v="2019-01-05T00:00:00"/>
+        <d v="2018-11-23T00:00:00"/>
+        <d v="2018-10-23T00:00:00"/>
+        <d v="2018-09-10T00:00:00"/>
+        <d v="2019-01-07T00:00:00"/>
+        <d v="2018-12-20T00:00:00"/>
+        <d v="2018-09-09T00:00:00"/>
+        <d v="2019-01-14T00:00:00"/>
+        <d v="2019-01-29T00:00:00"/>
+        <d v="2019-01-03T00:00:00"/>
+        <d v="2018-09-14T00:00:00"/>
+        <d v="2018-08-16T00:00:00"/>
+        <d v="2018-07-03T00:00:00"/>
+        <d v="2019-01-04T00:00:00"/>
+        <d v="2019-01-21T00:00:00"/>
+        <d v="2019-01-16T00:00:00"/>
+        <d v="2018-12-08T00:00:00"/>
+        <d v="2018-12-12T00:00:00"/>
+        <d v="2018-11-07T00:00:00"/>
+        <d v="2018-10-05T00:00:00"/>
+        <d v="2018-10-28T00:00:00"/>
+        <d v="2019-01-26T00:00:00"/>
+        <d v="2018-10-17T00:00:00"/>
+        <d v="2019-01-18T00:00:00"/>
+        <d v="2018-11-19T00:00:00"/>
+        <d v="2018-11-06T00:00:00"/>
+        <d v="2018-12-07T00:00:00"/>
+        <d v="2018-12-14T00:00:00"/>
+        <d v="2019-01-19T00:00:00"/>
+        <d v="2018-10-14T00:00:00"/>
+        <d v="2018-10-09T00:00:00"/>
+        <d v="2018-08-05T00:00:00"/>
+        <d v="2018-06-06T00:00:00"/>
+      </sharedItems>
+      <fieldGroup par="7"/>
+    </cacheField>
+    <cacheField name="Country" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Price" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.6060726263026939" maxValue="1254.4805452381811" count="38">
+        <n v="140.35435673674468"/>
+        <n v="45.07590782878367"/>
+        <n v="36.06"/>
+        <n v="16.45571141802796"/>
+        <n v="24.202757443534914"/>
+        <n v="106.47530441263088"/>
+        <n v="237.14735614775282"/>
+        <n v="145.19250417703412"/>
+        <n v="55.94220667604246"/>
+        <n v="84.213816066255575"/>
+        <n v="435.5775125311024"/>
+        <n v="203.268303823639"/>
+        <n v="300.06130323464714"/>
+        <n v="3.6060726263026939"/>
+        <n v="77.891168728138183"/>
+        <n v="193.39367494861347"/>
+        <n v="1254.4805452381811"/>
+        <n v="38.945584364069092"/>
+        <n v="93.036673758609496"/>
+        <n v="62.727633334535362"/>
+        <n v="36.595627035928501"/>
+        <n v="365.98031084346042"/>
+        <n v="470.41818422223025"/>
+        <n v="5.5233012392869592"/>
+        <n v="25.170386931592802"/>
+        <n v="20.332239491303355"/>
+        <n v="5.613453054944527"/>
+        <n v="9.4959912492637599"/>
+        <n v="7.5487120310603055"/>
+        <n v="18.390970394143739"/>
+        <n v="12.579183344752563"/>
+        <n v="132.87175603716659"/>
+        <n v="86.113014316108334"/>
+        <n v="368.78703737093264"/>
+        <n v="87.549433245585561"/>
+        <n v="119.75166179846862"/>
+        <n v="47.708340845984637"/>
+        <n v="33.133797314677921"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Months (Date)" numFmtId="0" databaseField="0">
+      <fieldGroup base="2">
+        <rangePr groupBy="months" startDate="2018-05-12T00:00:00" endDate="2019-01-30T00:00:00"/>
+        <groupItems count="14">
+          <s v="&lt;5/12/2018"/>
+          <s v="Jan"/>
+          <s v="Feb"/>
+          <s v="Mar"/>
+          <s v="Apr"/>
+          <s v="May"/>
+          <s v="Jun"/>
+          <s v="Jul"/>
+          <s v="Aug"/>
+          <s v="Sep"/>
+          <s v="Oct"/>
+          <s v="Nov"/>
+          <s v="Dec"/>
+          <s v="&gt;1/30/2019"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Quarters (Date)" numFmtId="0" databaseField="0">
+      <fieldGroup base="2">
+        <rangePr groupBy="quarters" startDate="2018-05-12T00:00:00" endDate="2019-01-30T00:00:00"/>
+        <groupItems count="6">
+          <s v="&lt;5/12/2018"/>
+          <s v="Qtr1"/>
+          <s v="Qtr2"/>
+          <s v="Qtr3"/>
+          <s v="Qtr4"/>
+          <s v="&gt;1/30/2019"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Years (Date)" numFmtId="0" databaseField="0">
+      <fieldGroup base="2">
+        <rangePr groupBy="years" startDate="2018-05-12T00:00:00" endDate="2019-01-30T00:00:00"/>
+        <groupItems count="4">
+          <s v="&lt;5/12/2018"/>
+          <s v="2018"/>
+          <s v="2019"/>
+          <s v="&gt;1/30/2019"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="38">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="China"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="China"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="China"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="Japan"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Spain"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="5"/>
+    <s v="China"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="6"/>
+    <s v="Italy"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="7"/>
+    <s v="Morocco"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="8"/>
+    <s v="Spain"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="9"/>
+    <s v="China"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="10"/>
+    <s v="Italy"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="11"/>
+    <x v="11"/>
+    <s v="Italy"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="12"/>
+    <x v="12"/>
+    <s v="Morocco"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="13"/>
+    <s v="Spain"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="14"/>
+    <x v="14"/>
+    <s v="USA"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="15"/>
+    <x v="15"/>
+    <s v="USA"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="16"/>
+    <x v="16"/>
+    <s v="Japan"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="17"/>
+    <x v="17"/>
+    <s v="Sweden"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="18"/>
+    <x v="18"/>
+    <s v="Morocco"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="19"/>
+    <x v="19"/>
+    <s v="Japan"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="20"/>
+    <x v="20"/>
+    <s v="Spain"/>
+    <x v="20"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="21"/>
+    <x v="21"/>
+    <s v="USA"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="22"/>
+    <x v="22"/>
+    <s v="USA"/>
+    <x v="22"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="23"/>
+    <s v="Spain"/>
+    <x v="23"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="24"/>
+    <x v="24"/>
+    <s v="France"/>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="25"/>
+    <x v="2"/>
+    <s v="USA"/>
+    <x v="25"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="26"/>
+    <x v="25"/>
+    <s v="Italy"/>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="27"/>
+    <x v="26"/>
+    <s v="Spain"/>
+    <x v="27"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="23"/>
+    <x v="27"/>
+    <s v="France"/>
+    <x v="28"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="28"/>
+    <s v="Spain"/>
+    <x v="29"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="29"/>
+    <x v="29"/>
+    <s v="Taiwan"/>
+    <x v="30"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="30"/>
+    <x v="30"/>
+    <s v="Morocco"/>
+    <x v="31"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="31"/>
+    <x v="31"/>
+    <s v="Japan"/>
+    <x v="32"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="32"/>
+    <x v="32"/>
+    <s v="USA"/>
+    <x v="33"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="33"/>
+    <x v="33"/>
+    <s v="Spain"/>
+    <x v="34"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="34"/>
+    <x v="34"/>
+    <s v="Japan"/>
+    <x v="35"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="35"/>
+    <x v="35"/>
+    <s v="Spain"/>
+    <x v="36"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="36"/>
+    <x v="36"/>
+    <s v="Turkey"/>
+    <x v="37"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EA5BDD41-C83C-4802-9659-78878AC8029C}" name="PivotTable13" cacheId="90" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:G11" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="38">
+        <item x="3"/>
+        <item x="19"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="29"/>
+        <item x="16"/>
+        <item x="4"/>
+        <item x="27"/>
+        <item x="24"/>
+        <item x="36"/>
+        <item x="28"/>
+        <item x="13"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="11"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="17"/>
+        <item x="0"/>
+        <item x="26"/>
+        <item x="30"/>
+        <item x="23"/>
+        <item x="18"/>
+        <item x="20"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="21"/>
+        <item x="2"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="32"/>
+        <item x="31"/>
+        <item x="33"/>
+        <item x="9"/>
+        <item x="12"/>
+        <item x="7"/>
+        <item x="25"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="38">
+        <item x="3"/>
+        <item x="36"/>
+        <item x="16"/>
+        <item x="35"/>
+        <item x="15"/>
+        <item x="10"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item x="23"/>
+        <item x="34"/>
+        <item x="33"/>
+        <item x="26"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="29"/>
+        <item x="22"/>
+        <item x="28"/>
+        <item x="5"/>
+        <item x="30"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="31"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="13"/>
+        <item x="17"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item x="2"/>
+        <item x="19"/>
+        <item x="27"/>
+        <item x="32"/>
+        <item x="18"/>
+        <item x="25"/>
+        <item x="0"/>
+        <item x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0">
+      <items count="39">
+        <item x="13"/>
+        <item x="23"/>
+        <item x="26"/>
+        <item x="28"/>
+        <item x="27"/>
+        <item x="30"/>
+        <item x="3"/>
+        <item x="29"/>
+        <item x="25"/>
+        <item x="4"/>
+        <item x="24"/>
+        <item x="37"/>
+        <item x="2"/>
+        <item x="20"/>
+        <item x="17"/>
+        <item x="1"/>
+        <item x="36"/>
+        <item x="8"/>
+        <item x="19"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="32"/>
+        <item x="34"/>
+        <item x="18"/>
+        <item x="5"/>
+        <item x="35"/>
+        <item x="31"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="15"/>
+        <item x="11"/>
+        <item x="6"/>
+        <item x="12"/>
+        <item x="21"/>
+        <item x="33"/>
+        <item x="10"/>
+        <item x="22"/>
+        <item x="16"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="2">
+    <field x="7"/>
+    <field x="-2"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x v="1"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+    <i t="grand" i="1">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sum of Price" fld="4" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name="Count of Section" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="14">
+    <format dxfId="15">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea field="7" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="7" count="2">
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="5">
+      <pivotArea field="7" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="3">
+      <pivotArea field="7" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="0">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="0" format="112" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="7" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="113" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="7" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="114" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="115" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -726,11 +8352,367 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93FF0705-CAE0-4ECD-B1B3-73270532710D}">
+  <dimension ref="A3:G24"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="10.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="11.21875" style="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="11.21875" style="13" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="10.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="11.21875" style="13" bestFit="1" customWidth="1"/>
+    <col min="26" max="29" width="9" style="13" bestFit="1" customWidth="1"/>
+    <col min="30" max="38" width="10.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="11.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="40" max="74" width="20.21875" style="13" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="18.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="76" max="77" width="17.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="78" max="16384" width="8.88671875" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="16">
+        <v>168.00692365944252</v>
+      </c>
+      <c r="C6" s="17">
+        <v>3</v>
+      </c>
+      <c r="D6" s="16">
+        <v>200.6171141802796</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3</v>
+      </c>
+      <c r="F6" s="16">
+        <v>368.62403783972212</v>
+      </c>
+      <c r="G6" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="16">
+        <v>902.13118892214493</v>
+      </c>
+      <c r="C7" s="17">
+        <v>4</v>
+      </c>
+      <c r="D7" s="16">
+        <v>562.87788636063124</v>
+      </c>
+      <c r="E7" s="17">
+        <v>4</v>
+      </c>
+      <c r="F7" s="16">
+        <v>1465.0090752827762</v>
+      </c>
+      <c r="G7" s="17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="16">
+        <v>71.15983315903982</v>
+      </c>
+      <c r="C8" s="17">
+        <v>5</v>
+      </c>
+      <c r="D8" s="16">
+        <v>33.494404577308188</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3</v>
+      </c>
+      <c r="F8" s="16">
+        <v>104.65423773634801</v>
+      </c>
+      <c r="G8" s="17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="16">
+        <v>2398.7595110165521</v>
+      </c>
+      <c r="C9" s="17">
+        <v>6</v>
+      </c>
+      <c r="D9" s="16">
+        <v>194.70989145721396</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3</v>
+      </c>
+      <c r="F9" s="16">
+        <v>2593.469402473766</v>
+      </c>
+      <c r="G9" s="17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="16">
+        <v>507.12800355799163</v>
+      </c>
+      <c r="C10" s="17">
+        <v>6</v>
+      </c>
+      <c r="D10" s="16">
+        <v>368.78703737093264</v>
+      </c>
+      <c r="E10" s="17">
+        <v>1</v>
+      </c>
+      <c r="F10" s="16">
+        <v>875.91504092892433</v>
+      </c>
+      <c r="G10" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="16">
+        <v>4047.185460315171</v>
+      </c>
+      <c r="C11" s="17">
+        <v>24</v>
+      </c>
+      <c r="D11" s="16">
+        <v>1360.4863339463657</v>
+      </c>
+      <c r="E11" s="17">
+        <v>14</v>
+      </c>
+      <c r="F11" s="16">
+        <v>5407.6717942615369</v>
+      </c>
+      <c r="G11" s="17">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18">
+        <v>2018</v>
+      </c>
+      <c r="D18" s="18">
+        <v>2019</v>
+      </c>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="21">
+        <f>SUMIFS(data!E2:E39, data!A2:A39, Sheet1!A19, data!F2:F39, 2018)</f>
+        <v>168.00692365944252</v>
+      </c>
+      <c r="C19" s="13">
+        <f>COUNTIFS(data!A2:A39, Sheet1!A19, data!F2:F39, 2018)</f>
+        <v>3</v>
+      </c>
+      <c r="D19" s="21">
+        <f>SUMIFS(data!E2:E39, data!A2:A39, Sheet1!A19, data!F2:F39, 2019)</f>
+        <v>200.6171141802796</v>
+      </c>
+      <c r="E19" s="19">
+        <f>COUNTIFS(data!A2:A39, Sheet1!A19, data!F2:F39, 2019)</f>
+        <v>3</v>
+      </c>
+      <c r="F19" s="21">
+        <f>SUM(B19,D19)</f>
+        <v>368.62403783972212</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="21">
+        <f>SUMIFS(data!E3:E40, data!A3:A40, Sheet1!A20, data!F3:F40, 2018)</f>
+        <v>902.13118892214493</v>
+      </c>
+      <c r="C20" s="13">
+        <f>COUNTIFS(data!A3:A40, Sheet1!A20, data!F3:F40, 2018)</f>
+        <v>4</v>
+      </c>
+      <c r="D20" s="21">
+        <f>SUMIFS(data!E3:E40, data!A3:A40, Sheet1!A20, data!F3:F40, 2019)</f>
+        <v>562.87788636063124</v>
+      </c>
+      <c r="E20" s="19">
+        <f>COUNTIFS(data!A3:A40, Sheet1!A20, data!F3:F40, 2019)</f>
+        <v>4</v>
+      </c>
+      <c r="F20" s="21">
+        <f t="shared" ref="F20:F23" si="0">SUM(B20,D20)</f>
+        <v>1465.0090752827762</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="21">
+        <f>SUMIFS(data!E4:E41, data!A4:A41, Sheet1!A21, data!F4:F41, 2018)</f>
+        <v>71.15983315903982</v>
+      </c>
+      <c r="C21" s="13">
+        <f>COUNTIFS(data!A4:A41, Sheet1!A21, data!F4:F41, 2018)</f>
+        <v>5</v>
+      </c>
+      <c r="D21" s="21">
+        <f>SUMIFS(data!E4:E41, data!A4:A41, Sheet1!A21, data!F4:F41, 2019)</f>
+        <v>33.494404577308188</v>
+      </c>
+      <c r="E21" s="19">
+        <f>COUNTIFS(data!A4:A41, Sheet1!A21, data!F4:F41, 2019)</f>
+        <v>3</v>
+      </c>
+      <c r="F21" s="21">
+        <f t="shared" si="0"/>
+        <v>104.65423773634801</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="21">
+        <f>SUMIFS(data!E5:E42, data!A5:A42, Sheet1!A22, data!F5:F42, 2018)</f>
+        <v>2398.7595110165521</v>
+      </c>
+      <c r="C22" s="13">
+        <f>COUNTIFS(data!A5:A42, Sheet1!A22, data!F5:F42, 2018)</f>
+        <v>6</v>
+      </c>
+      <c r="D22" s="21">
+        <f>SUMIFS(data!E5:E42, data!A5:A42, Sheet1!A22, data!F5:F42, 2019)</f>
+        <v>194.70989145721396</v>
+      </c>
+      <c r="E22" s="19">
+        <f>COUNTIFS(data!A5:A42, Sheet1!A22, data!F5:F42, 2019)</f>
+        <v>3</v>
+      </c>
+      <c r="F22" s="21">
+        <f t="shared" si="0"/>
+        <v>2593.469402473766</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="21">
+        <f>SUMIFS(data!E6:E43, data!A6:A43, Sheet1!A23, data!F6:F43, 2018)</f>
+        <v>507.12800355799163</v>
+      </c>
+      <c r="C23" s="13">
+        <f>COUNTIFS(data!A6:A43, Sheet1!A23, data!F6:F43, 2018)</f>
+        <v>6</v>
+      </c>
+      <c r="D23" s="21">
+        <f>SUMIFS(data!E6:E43, data!A6:A43, Sheet1!A23, data!F6:F43, 2019)</f>
+        <v>368.78703737093264</v>
+      </c>
+      <c r="E23" s="19">
+        <f>COUNTIFS(data!A6:A43, Sheet1!A23, data!F6:F43, 2019)</f>
+        <v>1</v>
+      </c>
+      <c r="F23" s="21">
+        <f t="shared" si="0"/>
+        <v>875.91504092892433</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="D20 D21:D23 B20:B23" formulaRange="1"/>
+  </ignoredErrors>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr applyStyles="1"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
@@ -751,7 +8733,7 @@
     <col min="44" max="60" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -767,8 +8749,11 @@
       <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="F1" s="20" t="s">
+        <v>72</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -784,8 +8769,12 @@
       <c r="E2" s="6">
         <v>140.35435673674468</v>
       </c>
+      <c r="F2">
+        <f>YEAR(C2)</f>
+        <v>2019</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -801,8 +8790,12 @@
       <c r="E3" s="6">
         <v>45.07590782878367</v>
       </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F39" si="0">YEAR(C3)</f>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -818,8 +8811,12 @@
       <c r="E4" s="6">
         <v>36.06</v>
       </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>2019</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
@@ -835,8 +8832,12 @@
       <c r="E5" s="6">
         <v>16.45571141802796</v>
       </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="6" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -852,8 +8853,12 @@
       <c r="E6" s="6">
         <v>24.202757443534914</v>
       </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>2019</v>
+      </c>
     </row>
-    <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
@@ -869,8 +8874,12 @@
       <c r="E7" s="6">
         <v>106.47530441263088</v>
       </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
@@ -886,8 +8895,12 @@
       <c r="E8" s="6">
         <v>237.14735614775282</v>
       </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
@@ -903,8 +8916,12 @@
       <c r="E9" s="6">
         <v>145.19250417703412</v>
       </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
@@ -920,8 +8937,12 @@
       <c r="E10" s="6">
         <v>55.94220667604246</v>
       </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>2019</v>
+      </c>
     </row>
-    <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
@@ -937,8 +8958,12 @@
       <c r="E11" s="6">
         <v>84.213816066255575</v>
       </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
@@ -954,8 +8979,12 @@
       <c r="E12" s="6">
         <v>435.5775125311024</v>
       </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
@@ -971,8 +9000,12 @@
       <c r="E13" s="6">
         <v>203.268303823639</v>
       </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>2019</v>
+      </c>
     </row>
-    <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -988,8 +9021,12 @@
       <c r="E14" s="6">
         <v>300.06130323464714</v>
       </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>2019</v>
+      </c>
     </row>
-    <row r="15" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
@@ -1005,8 +9042,12 @@
       <c r="E15" s="6">
         <v>3.6060726263026939</v>
       </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>2019</v>
+      </c>
     </row>
-    <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
@@ -1022,8 +9063,12 @@
       <c r="E16" s="6">
         <v>77.891168728138183</v>
       </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>14</v>
       </c>
@@ -1039,8 +9084,12 @@
       <c r="E17" s="6">
         <v>193.39367494861347</v>
       </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
@@ -1056,8 +9105,12 @@
       <c r="E18" s="6">
         <v>1254.4805452381811</v>
       </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>14</v>
       </c>
@@ -1073,8 +9126,12 @@
       <c r="E19" s="6">
         <v>38.945584364069092</v>
       </c>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>2019</v>
+      </c>
     </row>
-    <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>14</v>
       </c>
@@ -1090,8 +9147,12 @@
       <c r="E20" s="6">
         <v>93.036673758609496</v>
       </c>
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>2019</v>
+      </c>
     </row>
-    <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>14</v>
       </c>
@@ -1107,8 +9168,12 @@
       <c r="E21" s="6">
         <v>62.727633334535362</v>
       </c>
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>2019</v>
+      </c>
     </row>
-    <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>14</v>
       </c>
@@ -1124,8 +9189,12 @@
       <c r="E22" s="6">
         <v>36.595627035928501</v>
       </c>
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="23" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>14</v>
       </c>
@@ -1141,8 +9210,12 @@
       <c r="E23" s="6">
         <v>365.98031084346042</v>
       </c>
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
@@ -1158,8 +9231,12 @@
       <c r="E24" s="6">
         <v>470.41818422223025</v>
       </c>
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>15</v>
       </c>
@@ -1175,8 +9252,12 @@
       <c r="E25" s="6">
         <v>5.5233012392869592</v>
       </c>
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>15</v>
       </c>
@@ -1192,8 +9273,12 @@
       <c r="E26" s="6">
         <v>25.170386931592802</v>
       </c>
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>15</v>
       </c>
@@ -1209,8 +9294,12 @@
       <c r="E27" s="6">
         <v>20.332239491303355</v>
       </c>
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>2019</v>
+      </c>
     </row>
-    <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>15</v>
       </c>
@@ -1226,8 +9315,12 @@
       <c r="E28" s="6">
         <v>5.613453054944527</v>
       </c>
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>2019</v>
+      </c>
     </row>
-    <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>15</v>
       </c>
@@ -1243,8 +9336,12 @@
       <c r="E29" s="6">
         <v>9.4959912492637599</v>
       </c>
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>15</v>
       </c>
@@ -1260,8 +9357,12 @@
       <c r="E30" s="6">
         <v>7.5487120310603055</v>
       </c>
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>2019</v>
+      </c>
     </row>
-    <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>15</v>
       </c>
@@ -1277,8 +9378,12 @@
       <c r="E31" s="6">
         <v>18.390970394143739</v>
       </c>
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="32" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
@@ -1294,8 +9399,12 @@
       <c r="E32" s="6">
         <v>12.579183344752563</v>
       </c>
+      <c r="F32">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="33" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>16</v>
       </c>
@@ -1311,8 +9420,12 @@
       <c r="E33" s="6">
         <v>132.87175603716659</v>
       </c>
+      <c r="F33">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="34" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>16</v>
       </c>
@@ -1328,8 +9441,12 @@
       <c r="E34" s="6">
         <v>86.113014316108334</v>
       </c>
+      <c r="F34">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="35" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>16</v>
       </c>
@@ -1345,8 +9462,12 @@
       <c r="E35" s="6">
         <v>368.78703737093264</v>
       </c>
+      <c r="F35">
+        <f t="shared" si="0"/>
+        <v>2019</v>
+      </c>
     </row>
-    <row r="36" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>16</v>
       </c>
@@ -1362,8 +9483,12 @@
       <c r="E36" s="6">
         <v>87.549433245585561</v>
       </c>
+      <c r="F36">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="37" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>16</v>
       </c>
@@ -1379,8 +9504,12 @@
       <c r="E37" s="6">
         <v>119.75166179846862</v>
       </c>
+      <c r="F37">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="38" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>16</v>
       </c>
@@ -1396,8 +9525,12 @@
       <c r="E38" s="6">
         <v>47.708340845984637</v>
       </c>
+      <c r="F38">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
     </row>
-    <row r="39" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>16</v>
       </c>
@@ -1412,6 +9545,10 @@
       </c>
       <c r="E39" s="8">
         <v>33.133797314677921</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="0"/>
+        <v>2018</v>
       </c>
     </row>
   </sheetData>
